--- a/coronavirus_response_forms/017_pre_appointment_wellness_form--coronavirus_response_forms.xlsx
+++ b/coronavirus_response_forms/017_pre_appointment_wellness_form--coronavirus_response_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Have you had any close contact with anyone who has been diagnosed with COVID-19?</t>
+          <t>Exposure2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Have you had any close contact with anyone who has been exposed to COVID-19?</t>
+          <t>Exposure4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Have you had any close contact with anyone who has been diagnosed with COVID-19?</t>
+          <t>Exposure1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Have you had any close contact with prophets who has been exposed to COVID-19?</t>
+          <t>Exposure3 Pros</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Do you currently have any of the following symptoms?</t>
+          <t>Symptoms1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>travel1</t>
+          <t>travel1_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Have you traveled anywhere outside the city during the last 14 days?</t>
+          <t>Travel1 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -2831,7 +2831,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>travel1_choices</t>
+          <t>travel1_2_choices</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2848,7 +2848,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>travel1_choices</t>
+          <t>travel1_2_choices</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
